--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,6 +1399,1132 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120174193</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>292646</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521881</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120174167</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>292641</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521852</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120174179</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>292633</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6521859</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120174024</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>292624</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6521898</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120174014</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>292632</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6521919</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120173997</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>292657</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6521935</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120174261</v>
+      </c>
+      <c r="B14" t="n">
+        <v>94410</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>292583</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6521882</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120174164</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>292650</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6521840</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120174001</v>
+      </c>
+      <c r="B16" t="n">
+        <v>77866</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>292623</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6521918</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120174133</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Amundshatt, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>292687</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6521921</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120174193</v>
+        <v>120174261</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>94410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,39 +1413,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1453,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292646</v>
+        <v>292583</v>
       </c>
       <c r="R8" t="n">
-        <v>6521881</v>
+        <v>6521882</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1491,17 +1483,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1520,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120174167</v>
+        <v>120174024</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,35 +1520,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1568,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292641</v>
+        <v>292624</v>
       </c>
       <c r="R9" t="n">
-        <v>6521852</v>
+        <v>6521898</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1612,7 +1600,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1631,7 +1618,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120174179</v>
+        <v>120173997</v>
       </c>
       <c r="B10" t="n">
         <v>57326</v>
@@ -1679,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292633</v>
+        <v>292657</v>
       </c>
       <c r="R10" t="n">
-        <v>6521859</v>
+        <v>6521935</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1741,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174024</v>
+        <v>120174014</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,35 +1740,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1789,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292624</v>
+        <v>292632</v>
       </c>
       <c r="R11" t="n">
-        <v>6521898</v>
+        <v>6521919</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1833,6 +1820,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1851,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174014</v>
+        <v>120174001</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>77866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,35 +1851,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6443</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1899,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292632</v>
+        <v>292623</v>
       </c>
       <c r="R12" t="n">
-        <v>6521919</v>
+        <v>6521918</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1962,10 +1945,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173997</v>
+        <v>120174193</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,29 +1961,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2010,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292657</v>
+        <v>292646</v>
       </c>
       <c r="R13" t="n">
-        <v>6521935</v>
+        <v>6521881</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2046,6 +2033,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174261</v>
+        <v>120174133</v>
       </c>
       <c r="B14" t="n">
-        <v>94410</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,31 +2076,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2116,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292583</v>
+        <v>292687</v>
       </c>
       <c r="R14" t="n">
-        <v>6521882</v>
+        <v>6521921</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2154,13 +2162,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2179,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174164</v>
+        <v>120174179</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,16 +2207,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2217,7 +2229,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2227,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292650</v>
+        <v>292633</v>
       </c>
       <c r="R15" t="n">
-        <v>6521840</v>
+        <v>6521859</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2263,11 +2275,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174001</v>
+        <v>120174164</v>
       </c>
       <c r="B16" t="n">
-        <v>77866</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,30 +2313,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6443</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2337,10 +2349,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292623</v>
+        <v>292650</v>
       </c>
       <c r="R16" t="n">
-        <v>6521918</v>
+        <v>6521840</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2375,13 +2387,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2400,10 +2416,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174133</v>
+        <v>120174167</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,47 +2428,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2460,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292687</v>
+        <v>292641</v>
       </c>
       <c r="R17" t="n">
-        <v>6521921</v>
+        <v>6521852</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,17 +2502,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174001</v>
+        <v>120174193</v>
       </c>
       <c r="B12" t="n">
-        <v>77866</v>
+        <v>57463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,30 +1851,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6443</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1882,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292623</v>
+        <v>292646</v>
       </c>
       <c r="R12" t="n">
-        <v>6521918</v>
+        <v>6521881</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,13 +1929,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1945,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174193</v>
+        <v>120174001</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>77866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,39 +1970,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6443</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1997,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292646</v>
+        <v>292623</v>
       </c>
       <c r="R13" t="n">
-        <v>6521881</v>
+        <v>6521918</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2035,17 +2039,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174193</v>
+        <v>120174001</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>77866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,39 +1851,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6443</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1891,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292646</v>
+        <v>292623</v>
       </c>
       <c r="R12" t="n">
-        <v>6521881</v>
+        <v>6521918</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1929,17 +1920,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1958,10 +1945,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174001</v>
+        <v>120174193</v>
       </c>
       <c r="B13" t="n">
-        <v>77866</v>
+        <v>57463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1957,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6443</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2001,10 +1997,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292623</v>
+        <v>292646</v>
       </c>
       <c r="R13" t="n">
-        <v>6521918</v>
+        <v>6521881</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2039,13 +2035,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120174261</v>
+        <v>120173997</v>
       </c>
       <c r="B8" t="n">
-        <v>94410</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,31 +1413,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1445,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292583</v>
+        <v>292657</v>
       </c>
       <c r="R8" t="n">
-        <v>6521882</v>
+        <v>6521935</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1489,7 +1493,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,7 +1514,7 @@
         <v>120174024</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120173997</v>
+        <v>120174193</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,29 +1637,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1666,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292657</v>
+        <v>292646</v>
       </c>
       <c r="R10" t="n">
-        <v>6521935</v>
+        <v>6521881</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1702,6 +1709,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174014</v>
+        <v>120174164</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,35 +1752,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1776,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292632</v>
+        <v>292650</v>
       </c>
       <c r="R11" t="n">
-        <v>6521919</v>
+        <v>6521840</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1814,13 +1826,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1839,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174193</v>
+        <v>120174261</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>94433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,39 +1867,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1891,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292646</v>
+        <v>292583</v>
       </c>
       <c r="R12" t="n">
-        <v>6521881</v>
+        <v>6521882</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1929,17 +1937,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1958,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174001</v>
+        <v>120174014</v>
       </c>
       <c r="B13" t="n">
-        <v>77866</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,30 +1974,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6443</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2001,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292623</v>
+        <v>292632</v>
       </c>
       <c r="R13" t="n">
-        <v>6521918</v>
+        <v>6521919</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2064,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174133</v>
+        <v>120174001</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>77882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,47 +2085,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6443</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2124,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292687</v>
+        <v>292623</v>
       </c>
       <c r="R14" t="n">
-        <v>6521921</v>
+        <v>6521918</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2162,17 +2154,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174179</v>
+        <v>120174167</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,35 +2191,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2239,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292633</v>
+        <v>292641</v>
       </c>
       <c r="R15" t="n">
-        <v>6521859</v>
+        <v>6521852</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2283,6 +2271,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174164</v>
+        <v>120174179</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,16 +2306,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2339,7 +2328,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2349,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292650</v>
+        <v>292633</v>
       </c>
       <c r="R16" t="n">
-        <v>6521840</v>
+        <v>6521859</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2385,11 +2374,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174167</v>
+        <v>120174133</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,35 +2412,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2464,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292641</v>
+        <v>292687</v>
       </c>
       <c r="R17" t="n">
-        <v>6521852</v>
+        <v>6521921</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2502,13 +2498,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174014</v>
+        <v>120174001</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>77882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,35 +1974,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6443</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2010,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292632</v>
+        <v>292623</v>
       </c>
       <c r="R13" t="n">
-        <v>6521919</v>
+        <v>6521918</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174001</v>
+        <v>120174014</v>
       </c>
       <c r="B14" t="n">
-        <v>77882</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,30 +2080,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6443</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292623</v>
+        <v>292632</v>
       </c>
       <c r="R14" t="n">
-        <v>6521918</v>
+        <v>6521919</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173997</v>
+        <v>120174167</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,35 +1413,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292657</v>
+        <v>292641</v>
       </c>
       <c r="R8" t="n">
-        <v>6521935</v>
+        <v>6521852</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1493,6 +1493,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120174024</v>
+        <v>120174164</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,16 +1528,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1549,7 +1550,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1559,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292624</v>
+        <v>292650</v>
       </c>
       <c r="R9" t="n">
-        <v>6521898</v>
+        <v>6521840</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,6 +1596,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120174193</v>
+        <v>120174179</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,33 +1643,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1673,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292646</v>
+        <v>292633</v>
       </c>
       <c r="R10" t="n">
-        <v>6521881</v>
+        <v>6521859</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,11 +1711,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,7 +1737,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174164</v>
+        <v>120174133</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1773,9 +1770,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1788,10 +1797,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292650</v>
+        <v>292687</v>
       </c>
       <c r="R11" t="n">
-        <v>6521840</v>
+        <v>6521921</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1828,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174261</v>
+        <v>120174193</v>
       </c>
       <c r="B12" t="n">
-        <v>94433</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,31 +1876,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1899,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292583</v>
+        <v>292646</v>
       </c>
       <c r="R12" t="n">
-        <v>6521882</v>
+        <v>6521881</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1937,13 +1954,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1962,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174001</v>
+        <v>120173997</v>
       </c>
       <c r="B13" t="n">
-        <v>77882</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,30 +1995,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6443</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2005,10 +2031,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292623</v>
+        <v>292657</v>
       </c>
       <c r="R13" t="n">
-        <v>6521918</v>
+        <v>6521935</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2049,7 +2075,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2068,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174014</v>
+        <v>120174001</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>77882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2080,35 +2105,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6443</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2116,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292632</v>
+        <v>292623</v>
       </c>
       <c r="R14" t="n">
-        <v>6521919</v>
+        <v>6521918</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2179,7 +2199,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174167</v>
+        <v>120174014</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2214,7 +2234,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2227,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292641</v>
+        <v>292632</v>
       </c>
       <c r="R15" t="n">
-        <v>6521852</v>
+        <v>6521919</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2290,7 +2310,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174179</v>
+        <v>120174024</v>
       </c>
       <c r="B16" t="n">
         <v>57336</v>
@@ -2338,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292633</v>
+        <v>292624</v>
       </c>
       <c r="R16" t="n">
-        <v>6521859</v>
+        <v>6521898</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2400,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174133</v>
+        <v>120174261</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>94433</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,47 +2432,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2460,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292687</v>
+        <v>292583</v>
       </c>
       <c r="R17" t="n">
-        <v>6521921</v>
+        <v>6521882</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2498,17 +2502,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120174167</v>
+        <v>120173997</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,35 +1413,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292641</v>
+        <v>292657</v>
       </c>
       <c r="R8" t="n">
-        <v>6521852</v>
+        <v>6521935</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1493,7 +1493,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120174164</v>
+        <v>120174167</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,35 +1523,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1560,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292650</v>
+        <v>292641</v>
       </c>
       <c r="R9" t="n">
-        <v>6521840</v>
+        <v>6521852</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1598,17 +1597,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1737,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174133</v>
+        <v>120174001</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>77882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,47 +1744,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6443</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1797,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292687</v>
+        <v>292623</v>
       </c>
       <c r="R11" t="n">
-        <v>6521921</v>
+        <v>6521918</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1835,17 +1813,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1838,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174193</v>
+        <v>120174164</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,28 +1854,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
@@ -1916,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292646</v>
+        <v>292650</v>
       </c>
       <c r="R12" t="n">
-        <v>6521881</v>
+        <v>6521840</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1956,7 +1926,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett par I sitt permanenta revir</t>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120173997</v>
+        <v>120174193</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,29 +1969,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2031,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292657</v>
+        <v>292646</v>
       </c>
       <c r="R13" t="n">
-        <v>6521935</v>
+        <v>6521881</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2067,6 +2041,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174001</v>
+        <v>120174261</v>
       </c>
       <c r="B14" t="n">
-        <v>77882</v>
+        <v>94433</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,26 +2088,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6443</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2136,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292623</v>
+        <v>292583</v>
       </c>
       <c r="R14" t="n">
-        <v>6521918</v>
+        <v>6521882</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2310,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174024</v>
+        <v>120174133</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,16 +2306,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2343,12 +2323,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2358,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292624</v>
+        <v>292687</v>
       </c>
       <c r="R16" t="n">
-        <v>6521898</v>
+        <v>6521921</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2394,6 +2386,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174261</v>
+        <v>120174024</v>
       </c>
       <c r="B17" t="n">
-        <v>94433</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,31 +2429,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2464,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292583</v>
+        <v>292624</v>
       </c>
       <c r="R17" t="n">
-        <v>6521882</v>
+        <v>6521898</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2508,7 +2509,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173997</v>
+        <v>120174164</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292657</v>
+        <v>292650</v>
       </c>
       <c r="R8" t="n">
-        <v>6521935</v>
+        <v>6521840</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1485,6 +1485,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120174167</v>
+        <v>120173997</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,35 +1528,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1559,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292641</v>
+        <v>292657</v>
       </c>
       <c r="R9" t="n">
-        <v>6521852</v>
+        <v>6521935</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1603,7 +1608,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1622,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120174179</v>
+        <v>120174133</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,16 +1642,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1655,12 +1659,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1670,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292633</v>
+        <v>292687</v>
       </c>
       <c r="R10" t="n">
-        <v>6521859</v>
+        <v>6521921</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1706,6 +1722,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174001</v>
+        <v>120174024</v>
       </c>
       <c r="B11" t="n">
-        <v>77882</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,30 +1765,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6443</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1775,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292623</v>
+        <v>292624</v>
       </c>
       <c r="R11" t="n">
-        <v>6521918</v>
+        <v>6521898</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,7 +1845,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1838,10 +1863,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174164</v>
+        <v>120174193</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,24 +1879,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
@@ -1886,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292650</v>
+        <v>292646</v>
       </c>
       <c r="R12" t="n">
-        <v>6521840</v>
+        <v>6521881</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1926,7 +1955,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
+          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174193</v>
+        <v>120174014</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,39 +1994,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2005,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292646</v>
+        <v>292632</v>
       </c>
       <c r="R13" t="n">
-        <v>6521881</v>
+        <v>6521919</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2043,17 +2068,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2072,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174261</v>
+        <v>120174179</v>
       </c>
       <c r="B14" t="n">
-        <v>94433</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,31 +2105,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2116,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292583</v>
+        <v>292633</v>
       </c>
       <c r="R14" t="n">
-        <v>6521882</v>
+        <v>6521859</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2160,7 +2185,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2179,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174014</v>
+        <v>120174001</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>77882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,35 +2215,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2227,10 +2246,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292632</v>
+        <v>292623</v>
       </c>
       <c r="R15" t="n">
-        <v>6521919</v>
+        <v>6521918</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2290,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174133</v>
+        <v>120174167</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,47 +2321,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2350,10 +2357,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292687</v>
+        <v>292641</v>
       </c>
       <c r="R16" t="n">
-        <v>6521921</v>
+        <v>6521852</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2388,17 +2395,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174024</v>
+        <v>120174261</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>94433</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,35 +2432,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2465,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292624</v>
+        <v>292583</v>
       </c>
       <c r="R17" t="n">
-        <v>6521898</v>
+        <v>6521882</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2509,6 +2508,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120174164</v>
+        <v>120173997</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292650</v>
+        <v>292657</v>
       </c>
       <c r="R8" t="n">
-        <v>6521840</v>
+        <v>6521935</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1485,11 +1485,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120173997</v>
+        <v>120174164</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,16 +1527,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1564,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292657</v>
+        <v>292650</v>
       </c>
       <c r="R9" t="n">
-        <v>6521935</v>
+        <v>6521840</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1600,6 +1595,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120174133</v>
+        <v>120174001</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>77882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,47 +1638,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6443</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1686,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292687</v>
+        <v>292623</v>
       </c>
       <c r="R10" t="n">
-        <v>6521921</v>
+        <v>6521918</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1724,17 +1707,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1753,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174024</v>
+        <v>120174193</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,29 +1748,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1801,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292624</v>
+        <v>292646</v>
       </c>
       <c r="R11" t="n">
-        <v>6521898</v>
+        <v>6521881</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1837,6 +1820,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174193</v>
+        <v>120174167</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,39 +1863,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1915,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292646</v>
+        <v>292641</v>
       </c>
       <c r="R12" t="n">
-        <v>6521881</v>
+        <v>6521852</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1953,17 +1937,13 @@
           <t>2024-10-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1982,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174014</v>
+        <v>120174024</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,35 +1974,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2030,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292632</v>
+        <v>292624</v>
       </c>
       <c r="R13" t="n">
-        <v>6521919</v>
+        <v>6521898</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2074,7 +2054,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2203,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174001</v>
+        <v>120174133</v>
       </c>
       <c r="B15" t="n">
-        <v>77882</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,30 +2194,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6443</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2246,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292623</v>
+        <v>292687</v>
       </c>
       <c r="R15" t="n">
-        <v>6521918</v>
+        <v>6521921</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2284,13 +2280,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174167</v>
+        <v>120174261</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>94433</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2321,32 +2321,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -2357,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292641</v>
+        <v>292583</v>
       </c>
       <c r="R16" t="n">
-        <v>6521852</v>
+        <v>6521882</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2420,10 +2416,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174261</v>
+        <v>120174014</v>
       </c>
       <c r="B17" t="n">
-        <v>94433</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,28 +2428,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292583</v>
+        <v>292632</v>
       </c>
       <c r="R17" t="n">
-        <v>6521882</v>
+        <v>6521919</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120173997</v>
+        <v>120174164</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292657</v>
+        <v>292650</v>
       </c>
       <c r="R8" t="n">
-        <v>6521935</v>
+        <v>6521840</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1485,6 +1485,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120174164</v>
+        <v>120174024</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,16 +1532,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1559,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292650</v>
+        <v>292624</v>
       </c>
       <c r="R9" t="n">
-        <v>6521840</v>
+        <v>6521898</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,11 +1600,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1732,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174193</v>
+        <v>120174133</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,30 +1748,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1784,10 +1792,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292646</v>
+        <v>292687</v>
       </c>
       <c r="R11" t="n">
-        <v>6521881</v>
+        <v>6521921</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1824,7 +1832,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ett par I sitt permanenta revir</t>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,7 +1859,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174167</v>
+        <v>120174014</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1886,7 +1894,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1899,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292641</v>
+        <v>292632</v>
       </c>
       <c r="R12" t="n">
-        <v>6521852</v>
+        <v>6521919</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1962,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174024</v>
+        <v>120174167</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,35 +1982,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2010,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292624</v>
+        <v>292641</v>
       </c>
       <c r="R13" t="n">
-        <v>6521898</v>
+        <v>6521852</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2054,6 +2062,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2081,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120174179</v>
+        <v>120173997</v>
       </c>
       <c r="B14" t="n">
         <v>57336</v>
@@ -2120,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292633</v>
+        <v>292657</v>
       </c>
       <c r="R14" t="n">
-        <v>6521859</v>
+        <v>6521935</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2182,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174133</v>
+        <v>120174179</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,16 +2207,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2215,24 +2224,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2242,10 +2239,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292687</v>
+        <v>292633</v>
       </c>
       <c r="R15" t="n">
-        <v>6521921</v>
+        <v>6521859</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2278,11 +2275,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2416,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174014</v>
+        <v>120174193</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,35 +2420,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2464,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292632</v>
+        <v>292646</v>
       </c>
       <c r="R17" t="n">
-        <v>6521919</v>
+        <v>6521881</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2502,13 +2498,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -1401,7 +1401,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120174164</v>
+        <v>120174133</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1434,9 +1434,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1449,10 +1461,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>292650</v>
+        <v>292687</v>
       </c>
       <c r="R8" t="n">
-        <v>6521840</v>
+        <v>6521921</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1489,7 +1501,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hackspår, på flertalet träd inom reviret.</t>
+          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,7 +1528,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120174024</v>
+        <v>120173997</v>
       </c>
       <c r="B9" t="n">
         <v>57336</v>
@@ -1564,10 +1576,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>292624</v>
+        <v>292657</v>
       </c>
       <c r="R9" t="n">
-        <v>6521898</v>
+        <v>6521935</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1626,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120174001</v>
+        <v>120174014</v>
       </c>
       <c r="B10" t="n">
-        <v>77882</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1638,30 +1650,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6443</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>292623</v>
+        <v>292632</v>
       </c>
       <c r="R10" t="n">
-        <v>6521918</v>
+        <v>6521919</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1732,7 +1749,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120174133</v>
+        <v>120174164</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1765,21 +1782,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -1792,10 +1797,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>292687</v>
+        <v>292650</v>
       </c>
       <c r="R11" t="n">
-        <v>6521921</v>
+        <v>6521840</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1832,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födosök inom permanent revir, han lämnade färska hackmärken efter sig i en av de gamla granarna. Ganska unik för Bohuslän med så gamla granar. På alla är det riklig med gammelgranslav flera meter uppåt stammen vilket är mycket ovanlig i länet och indikerar mycket gamla träd. Området utgörs av gammal naturskog i nyckelbiotopsklass.</t>
+          <t>Hackspår, på flertalet träd inom reviret.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120174014</v>
+        <v>120174193</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,35 +1876,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1907,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>292632</v>
+        <v>292646</v>
       </c>
       <c r="R12" t="n">
-        <v>6521919</v>
+        <v>6521881</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,13 +1954,17 @@
           <t>2024-10-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett par I sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1970,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120174167</v>
+        <v>120174261</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>94433</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,32 +1995,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -2018,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>292641</v>
+        <v>292583</v>
       </c>
       <c r="R13" t="n">
-        <v>6521852</v>
+        <v>6521882</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2081,7 +2090,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120173997</v>
+        <v>120174179</v>
       </c>
       <c r="B14" t="n">
         <v>57336</v>
@@ -2129,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>292657</v>
+        <v>292633</v>
       </c>
       <c r="R14" t="n">
-        <v>6521935</v>
+        <v>6521859</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2191,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174179</v>
+        <v>120174167</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,35 +2212,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2239,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292633</v>
+        <v>292641</v>
       </c>
       <c r="R15" t="n">
-        <v>6521859</v>
+        <v>6521852</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2283,6 +2292,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174261</v>
+        <v>120174001</v>
       </c>
       <c r="B16" t="n">
-        <v>94433</v>
+        <v>77882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,27 +2327,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>6443</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2345,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292583</v>
+        <v>292623</v>
       </c>
       <c r="R16" t="n">
-        <v>6521882</v>
+        <v>6521918</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2408,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120174193</v>
+        <v>120174024</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,33 +2433,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2460,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>292646</v>
+        <v>292624</v>
       </c>
       <c r="R17" t="n">
-        <v>6521881</v>
+        <v>6521898</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2496,11 +2501,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett par I sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -2200,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120174167</v>
+        <v>120174001</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>77882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,35 +2212,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2248,10 +2243,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>292641</v>
+        <v>292623</v>
       </c>
       <c r="R15" t="n">
-        <v>6521852</v>
+        <v>6521918</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2311,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120174001</v>
+        <v>120174167</v>
       </c>
       <c r="B16" t="n">
-        <v>77882</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,30 +2318,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6443</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>292623</v>
+        <v>292641</v>
       </c>
       <c r="R16" t="n">
-        <v>6521918</v>
+        <v>6521852</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2525,6 +2525,132 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128757320</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56880</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tranemyr, Tranemyr, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>292666</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6521914</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Blev skrämd, bytte viloträd Bilden används för position- fågel ej på bild Träffat på tjäder i området fler ggr</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>128757320</v>
       </c>
       <c r="B18" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>128757320</v>
       </c>
       <c r="B18" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>128757320</v>
       </c>
       <c r="B18" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>128757320</v>
       </c>
       <c r="B18" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 1293-2021 artfynd.xlsx
+++ b/artfynd/A 1293-2021 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>128757320</v>
       </c>
       <c r="B18" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
